--- a/backend/superalloy_preprocess/annotated_data/CAST_Wrought_Alloys.xlsx
+++ b/backend/superalloy_preprocess/annotated_data/CAST_Wrought_Alloys.xlsx
@@ -22,6 +22,26 @@
   </definedNames>
   <calcPr/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="C59">
+      <text>
+        <t xml:space="preserve">@l.hawizy@digital-science.com the values from this column look quite low. Could you double-check please ?
+	-Alexandru Lecu
+you're right a lot of these are wrong let me update
+	-Lezan Hawizy
+good catch ive fixed all of them
+	-Lezan Hawizy</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29276,13 +29296,13 @@
         <v>78.0</v>
       </c>
       <c r="G12" s="5">
-        <v>12.0</v>
+        <v>128.0</v>
       </c>
       <c r="H12" s="5">
         <v>137.0</v>
       </c>
       <c r="I12" s="5">
-        <v>25.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="13">
@@ -29305,7 +29325,7 @@
         <v>84.0</v>
       </c>
       <c r="G13" s="5">
-        <v>11.0</v>
+        <v>118.0</v>
       </c>
       <c r="H13" s="5">
         <v>123.0</v>
@@ -29322,7 +29342,7 @@
         <v>151</v>
       </c>
       <c r="C14" s="5">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="D14" s="5">
         <v>50.0</v>
@@ -29334,7 +29354,7 @@
         <v>45.0</v>
       </c>
       <c r="G14" s="5">
-        <v>12.0</v>
+        <v>125.0</v>
       </c>
       <c r="H14" s="5">
         <v>155.0</v>
@@ -29465,7 +29485,7 @@
         <v>110.0</v>
       </c>
       <c r="G21" s="5">
-        <v>11.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="22">
@@ -29502,7 +29522,7 @@
         <v>151</v>
       </c>
       <c r="C23" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D23" s="5">
         <v>15.0</v>
@@ -29522,7 +29542,7 @@
         <v>151</v>
       </c>
       <c r="C24" s="5">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="D24" s="5">
         <v>15.0</v>
@@ -29545,7 +29565,7 @@
         <v>151</v>
       </c>
       <c r="C25" s="5">
-        <v>4.0</v>
+        <v>41.0</v>
       </c>
       <c r="D25" s="5">
         <v>40.0</v>
@@ -29571,7 +29591,7 @@
         <v>151</v>
       </c>
       <c r="C26" s="5">
-        <v>3.0</v>
+        <v>39.0</v>
       </c>
       <c r="D26" s="5">
         <v>37.0</v>
@@ -29628,7 +29648,7 @@
         <v>151</v>
       </c>
       <c r="C29" s="5">
-        <v>3.0</v>
+        <v>33.0</v>
       </c>
       <c r="D29" s="5">
         <v>28.0</v>
@@ -29654,7 +29674,7 @@
         <v>151</v>
       </c>
       <c r="C30" s="5">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="D30" s="5">
         <v>22.0</v>
@@ -29672,7 +29692,7 @@
         <v>37.0</v>
       </c>
       <c r="I30" s="5">
-        <v>32.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="31">
@@ -29683,7 +29703,7 @@
         <v>151</v>
       </c>
       <c r="C31" s="5">
-        <v>2.0</v>
+        <v>27.0</v>
       </c>
       <c r="D31" s="5">
         <v>18.0</v>
@@ -29709,7 +29729,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="5">
-        <v>3.0</v>
+        <v>39.0</v>
       </c>
       <c r="D32" s="5">
         <v>42.0</v>
@@ -29732,7 +29752,7 @@
         <v>129</v>
       </c>
       <c r="C33" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D33" s="5">
         <v>15.0</v>
@@ -29755,7 +29775,7 @@
         <v>151</v>
       </c>
       <c r="C34" s="5">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="D34" s="5">
         <v>12.0</v>
@@ -29775,7 +29795,7 @@
         <v>151</v>
       </c>
       <c r="C35" s="5">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
       <c r="D35" s="5">
         <v>23.0</v>
@@ -29795,7 +29815,7 @@
         <v>151</v>
       </c>
       <c r="C36" s="5">
-        <v>3.0</v>
+        <v>37.0</v>
       </c>
       <c r="D36" s="5">
         <v>26.0</v>
@@ -29818,7 +29838,7 @@
         <v>151</v>
       </c>
       <c r="C37" s="5">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="D37" s="5">
         <v>30.0</v>
@@ -29844,7 +29864,7 @@
         <v>151</v>
       </c>
       <c r="C38" s="5">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="D38" s="5">
         <v>15.0</v>
@@ -29864,7 +29884,7 @@
         <v>151</v>
       </c>
       <c r="C39" s="5">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="D39" s="5">
         <v>14.0</v>
@@ -29890,7 +29910,7 @@
         <v>152</v>
       </c>
       <c r="C40" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D40" s="5">
         <v>17.0</v>
@@ -29913,7 +29933,7 @@
         <v>158</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C41" s="5">
         <v>20.0</v>
@@ -29936,7 +29956,7 @@
         <v>151</v>
       </c>
       <c r="C42" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D42" s="5">
         <v>12.0</v>
@@ -29956,7 +29976,7 @@
         <v>151</v>
       </c>
       <c r="C43" s="5">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="D43" s="5">
         <v>12.0</v>
@@ -29979,7 +29999,7 @@
         <v>151</v>
       </c>
       <c r="C44" s="5">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="D44" s="5">
         <v>29.0</v>
@@ -30002,7 +30022,7 @@
         <v>151</v>
       </c>
       <c r="C45" s="5">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="D45" s="5">
         <v>14.0</v>
@@ -30031,7 +30051,7 @@
         <v>152</v>
       </c>
       <c r="C46" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D46" s="5">
         <v>6.0</v>
@@ -30063,7 +30083,7 @@
         <v>20.0</v>
       </c>
       <c r="D47" s="5">
-        <v>14.0</v>
+        <v>14.5</v>
       </c>
       <c r="E47" s="5">
         <v>11.0</v>
@@ -30089,7 +30109,7 @@
         <v>151</v>
       </c>
       <c r="C48" s="5">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="D48" s="5">
         <v>26.0</v>
@@ -30103,7 +30123,7 @@
         <v>151</v>
       </c>
       <c r="C49" s="5">
-        <v>3.0</v>
+        <v>32.0</v>
       </c>
       <c r="D49" s="5">
         <v>28.0</v>
@@ -30129,7 +30149,7 @@
         <v>151</v>
       </c>
       <c r="C50" s="5">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
       <c r="D50" s="5">
         <v>20.0</v>
@@ -30152,7 +30172,7 @@
         <v>151</v>
       </c>
       <c r="C51" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D51" s="5">
         <v>15.0</v>
@@ -30172,7 +30192,7 @@
         <v>151</v>
       </c>
       <c r="C52" s="5">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="D52" s="5">
         <v>16.0</v>
@@ -30252,7 +30272,7 @@
         <v>151</v>
       </c>
       <c r="C56" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D56" s="5">
         <v>14.0</v>
@@ -30278,7 +30298,7 @@
         <v>152</v>
       </c>
       <c r="C57" s="5">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="E57" s="5">
         <v>10.0</v>
@@ -30301,7 +30321,7 @@
         <v>151</v>
       </c>
       <c r="C58" s="5">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="D58" s="5">
         <v>23.0</v>
@@ -30318,6 +30338,7 @@
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$I$58"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>